--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,56 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,313 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>odds_home</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>odds_draw</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>odds_away</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>hK8xvrmh</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>rwisKhLu</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>2u7rIWkh</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>tW5nHj5b</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WA7tw22b</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MTkoJCzn</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>zg5jGAK4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ld9fFUZA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WKbaElkH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ABc3D84N</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vo27CSJT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tflZ7nSp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>raSHWV4o</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,286 +448,308 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.25</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -739,17 +739,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +753,276 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -752,276 +752,6 @@
           <t>7.00</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>jqf7smJ3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>G0IRHiWk</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fiHVGBod</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4nbBt7Y9</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>b9cFuRmG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zZKrObIr</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hAFmNIXl</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>QNDeLd21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>W0EiMxme</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>xbHaKGH7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>v3erq0f8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IgfnrK9E</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>nTbjsvPK</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>YyTMIXGq</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -739,17 +739,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,117 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6.00</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,161 +485,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.70</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -497,12 +497,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,68 +448,580 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>4.10</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>5.75</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -749,279 +749,9 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t>4.20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -448,95 +448,95 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -551,205 +551,205 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>4.20</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6.00</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2.70</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -744,14 +744,480 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -827,17 +827,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,144 +448,144 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>GvBXzXxS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>QHhnaCp6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>Iigr0hVa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>48ijbWaC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>dYh0Wjoq</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>nXtecjFI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>0zoadAUO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,629 +595,163 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>EwZtLg7P</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>GnL8GDFt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>zPi4VA0k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>YNFDFXUn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>6yELDBaa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>CEEHEipg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>4MWOCVE5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>W0zNyInr</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QJcftbvR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p4vRzx2l</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>88KCueOd</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>naJGvFw3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vRwVZeHf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>IHxZYFW0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>UN8LwZh9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>xlCTyDNL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>rRCPxg8F</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>z9yhkyHs</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4rtdleWm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>rZv0mFof</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>AoWGqXpJ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>QgE37zwQ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>n3Fa8GNJ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>rZ0V2fos</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>dx5Z1E0m</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>v1fv1YFg</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>SKZvN7pn</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>APpAklQ6</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>d0ReJPqB</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>0YXnLoFb</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>3.40</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -448,210 +448,210 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>3.60</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,14 +661,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -678,78 +678,78 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
+++ b/p6_deployment/data/usa/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
